--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Campañas\Campañas Würth Int\2026\Mundial Würth - Comprende todas las campañas hasta Julio inclusive\App\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FA5158-B853-46D4-A01D-3C847A6760A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E157DAE1-D396-4B1E-AC69-6869BFF152F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
@@ -144,7 +144,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +169,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -210,7 +216,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -226,6 +232,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,9 +574,9 @@
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.5703125" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="40.85546875" customWidth="1"/>
-    <col min="6" max="6" width="40.140625" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="6" width="40.85546875" customWidth="1"/>
     <col min="7" max="7" width="28.7109375" customWidth="1"/>
     <col min="8" max="8" width="39.28515625" customWidth="1"/>
     <col min="9" max="9" width="23.42578125" customWidth="1"/>
@@ -586,13 +593,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -614,7 +621,9 @@
       <c r="C2" s="6">
         <v>1.36</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="7">
+        <v>0.3</v>
+      </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -631,7 +640,9 @@
       <c r="C3" s="6">
         <v>0.65</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="7">
+        <v>0.5</v>
+      </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -648,7 +659,9 @@
       <c r="C4" s="6">
         <v>0.94</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="7">
+        <v>1.1479999999999999</v>
+      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -665,7 +678,9 @@
       <c r="C5" s="6">
         <v>0.79</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="7">
+        <v>0.222</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -682,7 +697,9 @@
       <c r="C6" s="6">
         <v>0.97</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="7">
+        <v>0.20699999999999999</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -699,7 +716,9 @@
       <c r="C7" s="6">
         <v>1.05</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="7">
+        <v>0.4</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -716,7 +735,9 @@
       <c r="C8" s="6">
         <v>1.02</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="7">
+        <v>0.192</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -733,7 +754,9 @@
       <c r="C9" s="6">
         <v>0.92</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="7">
+        <v>0.16700000000000001</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -750,7 +773,9 @@
       <c r="C10" s="6">
         <v>1.1299999999999999</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="7">
+        <v>0.19400000000000001</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -767,7 +792,9 @@
       <c r="C11" s="6">
         <v>0.83</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="7">
+        <v>0.44</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -784,7 +811,9 @@
       <c r="C12" s="6">
         <v>0.87</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="7">
+        <v>0.154</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -801,78 +830,80 @@
       <c r="C13" s="6">
         <v>0.82</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="7">
+        <v>0.625</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="2"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="5"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E157DAE1-D396-4B1E-AC69-6869BFF152F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5578D698-1C06-4FC2-B331-1FE6119E5283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
@@ -144,7 +144,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,12 +169,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -216,7 +210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -232,7 +226,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,7 +614,7 @@
       <c r="C2" s="6">
         <v>1.36</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>0.3</v>
       </c>
       <c r="E2" s="3"/>
@@ -640,7 +633,7 @@
       <c r="C3" s="6">
         <v>0.65</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>0.5</v>
       </c>
       <c r="E3" s="3"/>
@@ -659,7 +652,7 @@
       <c r="C4" s="6">
         <v>0.94</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>1.1479999999999999</v>
       </c>
       <c r="E4" s="3"/>
@@ -678,7 +671,7 @@
       <c r="C5" s="6">
         <v>0.79</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>0.222</v>
       </c>
       <c r="E5" s="3"/>
@@ -697,7 +690,7 @@
       <c r="C6" s="6">
         <v>0.97</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>0.20699999999999999</v>
       </c>
       <c r="E6" s="3"/>
@@ -716,7 +709,7 @@
       <c r="C7" s="6">
         <v>1.05</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>0.4</v>
       </c>
       <c r="E7" s="3"/>
@@ -735,7 +728,7 @@
       <c r="C8" s="6">
         <v>1.02</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>0.192</v>
       </c>
       <c r="E8" s="3"/>
@@ -754,7 +747,7 @@
       <c r="C9" s="6">
         <v>0.92</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>0.16700000000000001</v>
       </c>
       <c r="E9" s="3"/>
@@ -773,7 +766,7 @@
       <c r="C10" s="6">
         <v>1.1299999999999999</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>0.19400000000000001</v>
       </c>
       <c r="E10" s="3"/>
@@ -792,7 +785,7 @@
       <c r="C11" s="6">
         <v>0.83</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>0.44</v>
       </c>
       <c r="E11" s="3"/>
@@ -811,7 +804,7 @@
       <c r="C12" s="6">
         <v>0.87</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>0.154</v>
       </c>
       <c r="E12" s="3"/>
@@ -830,7 +823,7 @@
       <c r="C13" s="6">
         <v>0.82</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>0.625</v>
       </c>
       <c r="E13" s="3"/>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5578D698-1C06-4FC2-B331-1FE6119E5283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39191C0C-E939-4D83-AB63-879EECF7BA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
@@ -210,7 +210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -224,6 +224,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -614,7 +617,7 @@
       <c r="C2" s="6">
         <v>1.36</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="7">
         <v>0.3</v>
       </c>
       <c r="E2" s="3"/>
@@ -633,7 +636,7 @@
       <c r="C3" s="6">
         <v>0.65</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="7">
         <v>0.5</v>
       </c>
       <c r="E3" s="3"/>
@@ -652,7 +655,7 @@
       <c r="C4" s="6">
         <v>0.94</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="7">
         <v>1.1479999999999999</v>
       </c>
       <c r="E4" s="3"/>
@@ -671,7 +674,7 @@
       <c r="C5" s="6">
         <v>0.79</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <v>0.222</v>
       </c>
       <c r="E5" s="3"/>
@@ -690,7 +693,7 @@
       <c r="C6" s="6">
         <v>0.97</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <v>0.20699999999999999</v>
       </c>
       <c r="E6" s="3"/>
@@ -709,7 +712,7 @@
       <c r="C7" s="6">
         <v>1.05</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>0.4</v>
       </c>
       <c r="E7" s="3"/>
@@ -728,7 +731,7 @@
       <c r="C8" s="6">
         <v>1.02</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="7">
         <v>0.192</v>
       </c>
       <c r="E8" s="3"/>
@@ -747,7 +750,7 @@
       <c r="C9" s="6">
         <v>0.92</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>0.16700000000000001</v>
       </c>
       <c r="E9" s="3"/>
@@ -766,7 +769,7 @@
       <c r="C10" s="6">
         <v>1.1299999999999999</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>0.19400000000000001</v>
       </c>
       <c r="E10" s="3"/>
@@ -785,7 +788,7 @@
       <c r="C11" s="6">
         <v>0.83</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>0.44</v>
       </c>
       <c r="E11" s="3"/>
@@ -804,7 +807,7 @@
       <c r="C12" s="6">
         <v>0.87</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>0.154</v>
       </c>
       <c r="E12" s="3"/>
@@ -823,7 +826,7 @@
       <c r="C13" s="6">
         <v>0.82</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>0.625</v>
       </c>
       <c r="E13" s="3"/>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39191C0C-E939-4D83-AB63-879EECF7BA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7352596-FF49-494D-8EDA-369C30C52554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
@@ -226,7 +226,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7352596-FF49-494D-8EDA-369C30C52554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDF9ED1-BC89-4BAD-B5B5-94261DD8DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Equipo</t>
   </si>
@@ -135,6 +135,42 @@
   </si>
   <si>
     <t>Gustavo Silvera</t>
+  </si>
+  <si>
+    <t>30.0%</t>
+  </si>
+  <si>
+    <t>50.0%</t>
+  </si>
+  <si>
+    <t>114.8%</t>
+  </si>
+  <si>
+    <t>22.2%</t>
+  </si>
+  <si>
+    <t>20.7%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>19.2%</t>
+  </si>
+  <si>
+    <t>16.7%</t>
+  </si>
+  <si>
+    <t>19.4%</t>
+  </si>
+  <si>
+    <t>44.0%</t>
+  </si>
+  <si>
+    <t>15.4%</t>
+  </si>
+  <si>
+    <t>62.5%</t>
   </si>
 </sst>
 </file>
@@ -226,8 +262,8 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -617,8 +653,8 @@
       <c r="C2" s="6">
         <v>1.36</v>
       </c>
-      <c r="D2" s="7">
-        <v>0.3</v>
+      <c r="D2" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -636,8 +672,8 @@
       <c r="C3" s="6">
         <v>0.65</v>
       </c>
-      <c r="D3" s="7">
-        <v>0.5</v>
+      <c r="D3" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -655,8 +691,8 @@
       <c r="C4" s="6">
         <v>0.94</v>
       </c>
-      <c r="D4" s="7">
-        <v>1.1479999999999999</v>
+      <c r="D4" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -674,8 +710,8 @@
       <c r="C5" s="6">
         <v>0.79</v>
       </c>
-      <c r="D5" s="7">
-        <v>0.222</v>
+      <c r="D5" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -693,8 +729,8 @@
       <c r="C6" s="6">
         <v>0.97</v>
       </c>
-      <c r="D6" s="7">
-        <v>0.20699999999999999</v>
+      <c r="D6" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -712,8 +748,8 @@
       <c r="C7" s="6">
         <v>1.05</v>
       </c>
-      <c r="D7" s="7">
-        <v>0.4</v>
+      <c r="D7" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -731,8 +767,8 @@
       <c r="C8" s="6">
         <v>1.02</v>
       </c>
-      <c r="D8" s="7">
-        <v>0.192</v>
+      <c r="D8" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -750,8 +786,8 @@
       <c r="C9" s="6">
         <v>0.92</v>
       </c>
-      <c r="D9" s="7">
-        <v>0.16700000000000001</v>
+      <c r="D9" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -769,8 +805,8 @@
       <c r="C10" s="6">
         <v>1.1299999999999999</v>
       </c>
-      <c r="D10" s="7">
-        <v>0.19400000000000001</v>
+      <c r="D10" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -788,8 +824,8 @@
       <c r="C11" s="6">
         <v>0.83</v>
       </c>
-      <c r="D11" s="7">
-        <v>0.44</v>
+      <c r="D11" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -807,8 +843,8 @@
       <c r="C12" s="6">
         <v>0.87</v>
       </c>
-      <c r="D12" s="7">
-        <v>0.154</v>
+      <c r="D12" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -826,8 +862,8 @@
       <c r="C13" s="6">
         <v>0.82</v>
       </c>
-      <c r="D13" s="7">
-        <v>0.625</v>
+      <c r="D13" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDF9ED1-BC89-4BAD-B5B5-94261DD8DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD137E0C-4FA8-41DD-9F17-6A621399C0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Equipo</t>
   </si>
@@ -135,42 +135,6 @@
   </si>
   <si>
     <t>Gustavo Silvera</t>
-  </si>
-  <si>
-    <t>30.0%</t>
-  </si>
-  <si>
-    <t>50.0%</t>
-  </si>
-  <si>
-    <t>114.8%</t>
-  </si>
-  <si>
-    <t>22.2%</t>
-  </si>
-  <si>
-    <t>20.7%</t>
-  </si>
-  <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>19.2%</t>
-  </si>
-  <si>
-    <t>16.7%</t>
-  </si>
-  <si>
-    <t>19.4%</t>
-  </si>
-  <si>
-    <t>44.0%</t>
-  </si>
-  <si>
-    <t>15.4%</t>
-  </si>
-  <si>
-    <t>62.5%</t>
   </si>
 </sst>
 </file>
@@ -246,24 +210,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -600,21 +555,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5F107F-E25D-49E3-A8C0-030E9B4338FB}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.5703125" customWidth="1"/>
-    <col min="4" max="4" width="40.140625" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" customWidth="1"/>
-    <col min="6" max="6" width="40.85546875" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="5" width="40.85546875" customWidth="1"/>
+    <col min="6" max="6" width="40.140625" customWidth="1"/>
     <col min="7" max="7" width="28.7109375" customWidth="1"/>
     <col min="8" max="8" width="39.28515625" customWidth="1"/>
     <col min="9" max="9" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -625,13 +580,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -650,14 +605,14 @@
       <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="4">
         <v>1.36</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="F2" s="4">
+        <v>0.3</v>
+      </c>
       <c r="G2" s="3"/>
       <c r="H2" s="2"/>
       <c r="I2" s="3"/>
@@ -669,14 +624,14 @@
       <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
         <v>0.65</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4">
+        <v>0.5</v>
+      </c>
       <c r="G3" s="3"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3"/>
@@ -688,14 +643,14 @@
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>0.94</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>35</v>
-      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4">
+        <v>1.1479999999999999</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="2"/>
       <c r="I4" s="3"/>
@@ -707,14 +662,14 @@
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>0.79</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>36</v>
-      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4">
+        <v>0.222</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="2"/>
       <c r="I5" s="3"/>
@@ -726,14 +681,14 @@
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>0.97</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4">
+        <v>0.20699999999999999</v>
+      </c>
       <c r="G6" s="3"/>
       <c r="H6" s="2"/>
       <c r="I6" s="3"/>
@@ -745,14 +700,14 @@
       <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>1.05</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4">
+        <v>0.4</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="2"/>
       <c r="I7" s="3"/>
@@ -764,14 +719,14 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>1.02</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>39</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="4">
+        <v>0.192</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
       <c r="I8" s="3"/>
@@ -783,14 +738,14 @@
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>0.92</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="4">
+        <v>0.16700000000000001</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="2"/>
       <c r="I9" s="3"/>
@@ -802,14 +757,14 @@
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>1.1299999999999999</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="F10" s="4">
+        <v>0.19400000000000001</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="H10" s="2"/>
       <c r="I10" s="3"/>
@@ -821,14 +776,14 @@
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>0.83</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="F11" s="4">
+        <v>0.44</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="2"/>
       <c r="I11" s="3"/>
@@ -840,14 +795,14 @@
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>0.87</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>43</v>
-      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="F12" s="4">
+        <v>0.154</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="2"/>
       <c r="I12" s="3"/>
@@ -859,83 +814,17 @@
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <v>0.82</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>44</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="F13" s="4">
+        <v>0.625</v>
+      </c>
       <c r="G13" s="3"/>
       <c r="H13" s="2"/>
       <c r="I13" s="3"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD137E0C-4FA8-41DD-9F17-6A621399C0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A8FFBE-EB36-4240-80C3-5049632F0345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Equipo</t>
   </si>
@@ -135,6 +135,42 @@
   </si>
   <si>
     <t>Gustavo Silvera</t>
+  </si>
+  <si>
+    <t>114.8%</t>
+  </si>
+  <si>
+    <t>22.2%</t>
+  </si>
+  <si>
+    <t>20.7%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>19.2%</t>
+  </si>
+  <si>
+    <t>16.7</t>
+  </si>
+  <si>
+    <t>19.4%</t>
+  </si>
+  <si>
+    <t>44.0%</t>
+  </si>
+  <si>
+    <t>15.4%</t>
+  </si>
+  <si>
+    <t>62.5%</t>
+  </si>
+  <si>
+    <t>50.0%</t>
+  </si>
+  <si>
+    <t>30.0%</t>
   </si>
 </sst>
 </file>
@@ -610,8 +646,8 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="4">
-        <v>0.3</v>
+      <c r="F2" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="2"/>
@@ -629,8 +665,8 @@
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="4">
-        <v>0.5</v>
+      <c r="F3" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="2"/>
@@ -648,8 +684,8 @@
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="4">
-        <v>1.1479999999999999</v>
+      <c r="F4" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="2"/>
@@ -667,8 +703,8 @@
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="4">
-        <v>0.222</v>
+      <c r="F5" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="2"/>
@@ -686,8 +722,8 @@
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="4">
-        <v>0.20699999999999999</v>
+      <c r="F6" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="2"/>
@@ -705,8 +741,8 @@
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="4">
-        <v>0.4</v>
+      <c r="F7" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="2"/>
@@ -724,8 +760,8 @@
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="4">
-        <v>0.192</v>
+      <c r="F8" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
@@ -743,8 +779,8 @@
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="4">
-        <v>0.16700000000000001</v>
+      <c r="F9" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="2"/>
@@ -762,8 +798,8 @@
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="4">
-        <v>0.19400000000000001</v>
+      <c r="F10" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="2"/>
@@ -781,8 +817,8 @@
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="4">
-        <v>0.44</v>
+      <c r="F11" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="2"/>
@@ -800,8 +836,8 @@
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="4">
-        <v>0.154</v>
+      <c r="F12" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="2"/>
@@ -819,8 +855,8 @@
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="4">
-        <v>0.625</v>
+      <c r="F13" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="2"/>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A8FFBE-EB36-4240-80C3-5049632F0345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FAEA61-93B0-4B01-B1CF-A39598E7CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
@@ -137,40 +137,40 @@
     <t>Gustavo Silvera</t>
   </si>
   <si>
-    <t>114.8%</t>
-  </si>
-  <si>
-    <t>22.2%</t>
-  </si>
-  <si>
-    <t>20.7%</t>
-  </si>
-  <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>19.2%</t>
-  </si>
-  <si>
-    <t>16.7</t>
-  </si>
-  <si>
-    <t>19.4%</t>
-  </si>
-  <si>
-    <t>44.0%</t>
-  </si>
-  <si>
-    <t>15.4%</t>
-  </si>
-  <si>
-    <t>62.5%</t>
-  </si>
-  <si>
-    <t>50.0%</t>
-  </si>
-  <si>
-    <t>30.0%</t>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>0.1148</t>
+  </si>
+  <si>
+    <t>0.222</t>
+  </si>
+  <si>
+    <t>0.207</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>0.192</t>
+  </si>
+  <si>
+    <t>0.167</t>
+  </si>
+  <si>
+    <t>0.194</t>
+  </si>
+  <si>
+    <t>0.440</t>
+  </si>
+  <si>
+    <t>0.625</t>
+  </si>
+  <si>
+    <t>0.154</t>
+  </si>
+  <si>
+    <t>0.30</t>
   </si>
 </sst>
 </file>
@@ -246,7 +246,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -254,6 +254,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -646,7 +649,7 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>44</v>
       </c>
       <c r="G2" s="3"/>
@@ -665,8 +668,8 @@
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="4" t="s">
-        <v>43</v>
+      <c r="F3" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="2"/>
@@ -684,8 +687,8 @@
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="4" t="s">
-        <v>33</v>
+      <c r="F4" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="2"/>
@@ -703,8 +706,8 @@
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="4" t="s">
-        <v>34</v>
+      <c r="F5" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="2"/>
@@ -722,8 +725,8 @@
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="4" t="s">
-        <v>35</v>
+      <c r="F6" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="2"/>
@@ -741,8 +744,8 @@
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="4" t="s">
-        <v>36</v>
+      <c r="F7" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="2"/>
@@ -760,8 +763,8 @@
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="4" t="s">
-        <v>37</v>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
@@ -779,8 +782,8 @@
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="4" t="s">
-        <v>38</v>
+      <c r="F9" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="2"/>
@@ -798,8 +801,8 @@
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="4" t="s">
-        <v>39</v>
+      <c r="F10" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="2"/>
@@ -817,8 +820,8 @@
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="4" t="s">
-        <v>40</v>
+      <c r="F11" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="2"/>
@@ -836,8 +839,8 @@
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="4" t="s">
-        <v>41</v>
+      <c r="F12" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="2"/>
@@ -855,7 +858,7 @@
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>42</v>
       </c>
       <c r="G13" s="3"/>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FAEA61-93B0-4B01-B1CF-A39598E7CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DE6506-3AA5-46AA-B2E2-D72CF10DB560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Equipo</t>
   </si>
@@ -138,9 +138,6 @@
   </si>
   <si>
     <t>0.50</t>
-  </si>
-  <si>
-    <t>0.1148</t>
   </si>
   <si>
     <t>0.222</t>
@@ -246,7 +243,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -258,6 +255,9 @@
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -650,7 +650,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="2"/>
@@ -687,8 +687,8 @@
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="5" t="s">
-        <v>34</v>
+      <c r="F4" s="6">
+        <v>1148</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="2"/>
@@ -707,7 +707,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="2"/>
@@ -726,7 +726,7 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="2"/>
@@ -745,7 +745,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="2"/>
@@ -764,7 +764,7 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
@@ -783,7 +783,7 @@
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="2"/>
@@ -802,7 +802,7 @@
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="2"/>
@@ -821,7 +821,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="2"/>
@@ -840,7 +840,7 @@
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="2"/>
@@ -859,7 +859,7 @@
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="2"/>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DE6506-3AA5-46AA-B2E2-D72CF10DB560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07866993-93F3-4B8E-9894-0E78B54A95B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Equipo</t>
   </si>
@@ -135,39 +135,6 @@
   </si>
   <si>
     <t>Gustavo Silvera</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>0.222</t>
-  </si>
-  <si>
-    <t>0.207</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>0.192</t>
-  </si>
-  <si>
-    <t>0.167</t>
-  </si>
-  <si>
-    <t>0.194</t>
-  </si>
-  <si>
-    <t>0.440</t>
-  </si>
-  <si>
-    <t>0.625</t>
-  </si>
-  <si>
-    <t>0.154</t>
-  </si>
-  <si>
-    <t>0.30</t>
   </si>
 </sst>
 </file>
@@ -243,7 +210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -253,11 +220,8 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -649,8 +613,8 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="5" t="s">
-        <v>43</v>
+      <c r="F2" s="5">
+        <v>30</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="2"/>
@@ -668,8 +632,8 @@
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="5" t="s">
-        <v>33</v>
+      <c r="F3" s="5">
+        <v>50</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="2"/>
@@ -687,8 +651,8 @@
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="6">
-        <v>1148</v>
+      <c r="F4" s="5">
+        <v>115</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="2"/>
@@ -706,8 +670,8 @@
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="5" t="s">
-        <v>34</v>
+      <c r="F5" s="5">
+        <v>22</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="2"/>
@@ -725,8 +689,8 @@
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="5" t="s">
-        <v>35</v>
+      <c r="F6" s="5">
+        <v>21</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="2"/>
@@ -744,8 +708,8 @@
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="5" t="s">
-        <v>36</v>
+      <c r="F7" s="5">
+        <v>40</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="2"/>
@@ -763,8 +727,8 @@
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="5" t="s">
-        <v>37</v>
+      <c r="F8" s="5">
+        <v>19</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
@@ -782,8 +746,8 @@
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="5" t="s">
-        <v>38</v>
+      <c r="F9" s="5">
+        <v>17</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="2"/>
@@ -801,8 +765,8 @@
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="5" t="s">
-        <v>39</v>
+      <c r="F10" s="5">
+        <v>19</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="2"/>
@@ -820,8 +784,8 @@
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="5" t="s">
-        <v>40</v>
+      <c r="F11" s="5">
+        <v>44</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="2"/>
@@ -839,8 +803,8 @@
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="5" t="s">
-        <v>42</v>
+      <c r="F12" s="5">
+        <v>15</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="2"/>
@@ -858,8 +822,8 @@
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="5" t="s">
-        <v>41</v>
+      <c r="F13" s="5">
+        <v>63</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="2"/>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07866993-93F3-4B8E-9894-0E78B54A95B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152D4C4A-A427-4589-B314-272BE77B17FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
@@ -141,10 +141,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,13 +174,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -210,7 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -223,6 +242,11 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -611,7 +635,9 @@
       <c r="C2" s="4">
         <v>1.36</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="8">
+        <v>82.8</v>
+      </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5">
         <v>30</v>
@@ -630,7 +656,9 @@
       <c r="C3" s="4">
         <v>0.65</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="9">
+        <v>69</v>
+      </c>
       <c r="E3" s="3"/>
       <c r="F3" s="5">
         <v>50</v>
@@ -649,7 +677,9 @@
       <c r="C4" s="4">
         <v>0.94</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="8">
+        <v>85.3</v>
+      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5">
         <v>115</v>
@@ -668,7 +698,9 @@
       <c r="C5" s="4">
         <v>0.79</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="8">
+        <v>109</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5">
         <v>22</v>
@@ -687,7 +719,9 @@
       <c r="C6" s="4">
         <v>0.97</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="8">
+        <v>76.8</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="5">
         <v>21</v>
@@ -706,7 +740,9 @@
       <c r="C7" s="4">
         <v>1.05</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="8">
+        <v>90.4</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5">
         <v>40</v>
@@ -725,7 +761,9 @@
       <c r="C8" s="4">
         <v>1.02</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="8">
+        <v>86.5</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="5">
         <v>19</v>
@@ -744,7 +782,9 @@
       <c r="C9" s="4">
         <v>0.92</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="8">
+        <v>99.4</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5">
         <v>17</v>
@@ -763,7 +803,9 @@
       <c r="C10" s="4">
         <v>1.1299999999999999</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="8">
+        <v>78.599999999999994</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5">
         <v>19</v>
@@ -773,23 +815,25 @@
       <c r="I10" s="3"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="4">
         <v>0.83</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6"/>
       <c r="F11" s="5">
         <v>44</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -801,7 +845,9 @@
       <c r="C12" s="4">
         <v>0.87</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="8">
+        <v>98.9</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5">
         <v>15</v>
@@ -820,7 +866,9 @@
       <c r="C13" s="4">
         <v>0.82</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="8">
+        <v>96.8</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5">
         <v>63</v>

--- a/Planilla_Wurth_World_Cup_2026.xlsx
+++ b/Planilla_Wurth_World_Cup_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Campaña Würth World Cup APP\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152D4C4A-A427-4589-B314-272BE77B17FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEB1808-6A57-4264-83FE-AE3BD4F60441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4845B6FB-6455-4915-85AD-192BD8A40A56}"/>
   </bookViews>
@@ -119,9 +119,6 @@
     <t>Guillermo Pelaez</t>
   </si>
   <si>
-    <t>Equipo Naya</t>
-  </si>
-  <si>
     <t>Oscar Naya</t>
   </si>
   <si>
@@ -135,6 +132,9 @@
   </si>
   <si>
     <t>Gustavo Silvera</t>
+  </si>
+  <si>
+    <t>Equipo Naya (desc.)</t>
   </si>
 </sst>
 </file>
@@ -816,10 +816,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="C11" s="4">
         <v>0.83</v>
@@ -837,10 +837,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C12" s="4">
         <v>0.87</v>
@@ -858,10 +858,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C13" s="4">
         <v>0.82</v>
